--- a/國立臺北藝術大學招生自填資料匯入範本.xlsx
+++ b/國立臺北藝術大學招生自填資料匯入範本.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填寫資料" sheetId="1" r:id="R98e3ad9e27de4ad7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="範例與說明" sheetId="2" r:id="R074b36c57c7e42c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="欄位字典" sheetId="3" r:id="Rca244026d7d3451f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填寫資料" sheetId="1" r:id="Rcc3bf74b5a7247af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="範例與說明" sheetId="2" r:id="Rc92ac2ca0a3c4bd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="欄位字典" sheetId="3" r:id="Ree172cfa81a14e30"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5756,7 +5756,7 @@
       <x:formula2>130</x:formula2>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="D6:D155">
-      <x:formula1>"學士班（一般招生）,七年一貫制,學士後學士（歷史）,研究所總計,碩士班,碩士在職專班,博士班"</x:formula1>
+      <x:formula1>"學士班,七年一貫制,學士後學士（歷史）,研究所總計,碩士班,碩士在職專班,博士班"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="whole" operator="between" sqref="G6:K155">
       <x:formula1>0</x:formula1>
@@ -5771,7 +5771,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R382c52e18ff945c4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06acee53730948de"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5985,7 +5985,7 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="D11" s="112" t="str">
-        <x:v>學士班（一般招生）</x:v>
+        <x:v>學士班</x:v>
       </x:c>
       <x:c r="E11" s="112" t="str">
         <x:v>全校</x:v>
@@ -6025,7 +6025,7 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="D12" s="112" t="str">
-        <x:v>學士班（一般招生）</x:v>
+        <x:v>學士班</x:v>
       </x:c>
       <x:c r="E12" s="112" t="str">
         <x:v>音樂學院</x:v>
@@ -6196,7 +6196,7 @@
         <x:v>儀表板主要分析維度</x:v>
       </x:c>
       <x:c r="E8" s="104" t="str">
-        <x:v>學士班（一般招生）</x:v>
+        <x:v>學士班</x:v>
       </x:c>
       <x:c r="F8" s="104" t="str">
         <x:v>請使用範本選單</x:v>
